--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="633">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -634,604 +634,1282 @@
     <t>NSE:AXISBANK-EQ</t>
   </si>
   <si>
+    <t>2026-03-02 09:15</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:45</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:30</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:45</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:45</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:15</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:30</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:30</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:30</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:45</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:30</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:00</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:45</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:00</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:15</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:00</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:45</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:15</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:30</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:00</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1771828200_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1771822800_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BEAR_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ_BEAR_1771821000_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ_BULL_1771825500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:00</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:00</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ_BEAR_1771832700_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BULL_1771819200_1771911000</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:00</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ_BEAR_1771836300_1771913700</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:15</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BEAR_1771836300_1771914600</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:30</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771818300_1771915500</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:45</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ_BEAR_1771830900_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BULL_1771907400_1771918200</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:45</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1771904700_1771920000</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:00</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1771920900</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:45</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ_BULL_1771819200_1771920900</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:30</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771838100_1771922700</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:15</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ_BEAR_1771911000_1771923600</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771923600</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1771909200_1771925400</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771918200_1771925400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BULL_1771821900_1771926300</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:00</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BULL_1771908300_1771926300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771991100</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771991100</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:00</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ_BULL_1771925400_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:15</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1771912800_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:45</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ_BULL_1771905600_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771992900</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:30</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1771992000_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:30</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1771923600_1771999200</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:15</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ_BEAR_1771906500_1772001900</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:45</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BULL_1771907400_1772001900</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ_BEAR_1771905600_1772002800</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:00</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771904700_1772003700</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:15</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ_BULL_1771994700_1772004600</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:15</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ_BEAR_1771911000_1772005500</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:45</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1771991100_1772007300</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:45</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772008200</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771925400_1772009100</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:15</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BULL_1771997400_1772009100</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1771992900_1772010000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1772012700</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:00</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1771999200_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BEAR_1772003700_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:30</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:45</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1771997400_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:45</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BULL_1771994700_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:15</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772010000_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:15</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BULL_1771996500_1772079300</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771993800_1772079300</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:15</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1771994700_1772081100</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772081100</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771992000_1772082000</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:30</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ_BEAR_1772007300_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:45</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BULL_1772009100_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BEAR_1772002800_1772090100</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:15</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ_BULL_1772077500_1772091900</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:15</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:00</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:00</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1772091900_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BEAR_1772082900_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1772087400_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BEAR_1772085600_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BEAR_1772088300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ_BEAR_1772081100_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1772086500_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1772089200_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ_BULL_1772097300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:15</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ_BEAR_1772088300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1772079300_1772164800</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:30</t>
+  </si>
+  <si>
+    <t>NSE:RECLTD-EQ_BEAR_1772086500_1772165700</t>
+  </si>
+  <si>
+    <t>NSE:RECLTD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:15</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BEAR_1772082000_1772166600</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BEAR_1772088300_1772166600</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1772164800_1772169300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BEAR_1772165700_1772171100</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:45</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ_BEAR_1772077500_1772175600</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:30</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:00</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1772165700_1772176500</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:15</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772180100</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:15</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:30</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BEAR_1772095500_1772181900</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:45</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1772180100_1772183700</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:15</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:00</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BEAR_1772085600_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ_BEAR_1772167500_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1772163900_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1772091900_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ_BEAR_1772166600_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ_BEAR_1772164800_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BEAR_1772088300_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ_BEAR_1772099100_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1772170200_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772185500</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1772167500_1772185500</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:30</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 73 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:30</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 09:45</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:30</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 09:45</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:45</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 09:15</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:30</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:30</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:00</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:45</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:30</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:00</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:45</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:45</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:00</t>
-  </si>
-  <si>
-    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
-  </si>
-  <si>
-    <t>NSE:POWERGRID-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 15:15</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:00</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:45</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:15</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 09:30</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
-  </si>
-  <si>
-    <t>2026-02-23 15:00</t>
-  </si>
-  <si>
-    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
-  </si>
-  <si>
-    <t>NSE:APOLLOHOSP-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:ABCAPITAL-EQ_BEAR_1771828200_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ABCAPITAL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BDL-EQ_BEAR_1771822800_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:BDL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ_BEAR_1771834500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ITC-EQ_BEAR_1771821000_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ITC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IOC-EQ_BULL_1771825500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:IOC-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 15:00</t>
-  </si>
-  <si>
-    <t>NSE:OIL-EQ_BULL_1771834500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:OIL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:00</t>
-  </si>
-  <si>
-    <t>NSE:SBICARD-EQ_BEAR_1771832700_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:SBICARD-EQ</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ_BULL_1771819200_1771911000</t>
-  </si>
-  <si>
-    <t>2026-02-24 11:00</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:00</t>
-  </si>
-  <si>
-    <t>NSE:PATANJALI-EQ_BEAR_1771836300_1771913700</t>
-  </si>
-  <si>
-    <t>NSE:PATANJALI-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 11:45</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:15</t>
-  </si>
-  <si>
-    <t>NSE:POLICYBZR-EQ_BEAR_1771836300_1771914600</t>
-  </si>
-  <si>
-    <t>NSE:POLICYBZR-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:30</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BEAR_1771818300_1771915500</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:45</t>
-  </si>
-  <si>
-    <t>NSE:SHREECEM-EQ_BEAR_1771830900_1771917300</t>
-  </si>
-  <si>
-    <t>NSE:SHREECEM-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771821000_1771917300</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BULL_1771907400_1771918200</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:00</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:45</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1771904700_1771920000</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:30</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:00</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1771910100_1771920900</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:45</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ_BULL_1771819200_1771920900</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:30</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BEAR_1771838100_1771922700</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:15</t>
-  </si>
-  <si>
-    <t>NSE:HDFCBANK-EQ_BEAR_1771911000_1771923600</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771923600</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1771910100_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 15:15</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICHSGFIN-EQ_BULL_1771907400_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:LICHSGFIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1771907400_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BRITANNIA-EQ_BULL_1771909200_1771925400</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1771918200_1771925400</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ_BULL_1771821900_1771926300</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:00</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BULL_1771908300_1771926300</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771991100</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:15</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771991100</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:00</t>
-  </si>
-  <si>
-    <t>NSE:PETRONET-EQ_BULL_1771925400_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:PETRONET-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 11:15</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ_BULL_1771912800_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:45</t>
-  </si>
-  <si>
-    <t>NSE:TATASTEEL-EQ_BULL_1771905600_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:TATASTEEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1771907400_1771992900</t>
-  </si>
-  <si>
-    <t>2026-02-25 09:45</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:30</t>
-  </si>
-  <si>
-    <t>NSE:HEROMOTOCO-EQ_BULL_1771992000_1771999200</t>
-  </si>
-  <si>
-    <t>NSE:HEROMOTOCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 11:30</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:30</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ_BULL_1771921800_1771999200</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BULL_1771923600_1771999200</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:15</t>
-  </si>
-  <si>
-    <t>NSE:IRCTC-EQ_BEAR_1771906500_1772001900</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:45</t>
-  </si>
-  <si>
-    <t>NSE:PIDILITIND-EQ_BULL_1771907400_1772001900</t>
-  </si>
-  <si>
-    <t>NSE:PAYTM-EQ_BEAR_1771905600_1772002800</t>
-  </si>
-  <si>
-    <t>NSE:PAYTM-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:00</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ_BEAR_1771904700_1772003700</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:15</t>
-  </si>
-  <si>
-    <t>NSE:360ONE-EQ_BULL_1771994700_1772004600</t>
-  </si>
-  <si>
-    <t>NSE:360ONE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:15</t>
-  </si>
-  <si>
-    <t>NSE:ASIANPAINT-EQ_BEAR_1771911000_1772005500</t>
-  </si>
-  <si>
-    <t>NSE:ASIANPAINT-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:45</t>
-  </si>
-  <si>
-    <t>NSE:SAMMAANCAP-EQ_BULL_1771991100_1772007300</t>
-  </si>
-  <si>
-    <t>NSE:SAMMAANCAP-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:45</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BULL_1771991100_1772008200</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:00</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BULL_1771925400_1772009100</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:15</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ_BULL_1771997400_1772009100</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:00</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BULL_1771992900_1772010000</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
+    <t>Checked 99 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:00</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ_BEAR_1772167500_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:30</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772432100</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:15</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ_BEAR_1772164800_1772432100</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1772423100_1772433000</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:30</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ_BEAR_1772185500_1772433000</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1772163900_1772433900</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:45</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BEAR_1772184600_1772433900</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:00</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1772167500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BEAR_1772424000_1772436600</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:30</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BEAR_1772185500_1772437500</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:15</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:45</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1772423100_1772437500</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772439300</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BEAR_1772423100_1772442900</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-02 15:15</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1772431200_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772597700</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:15</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:15</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1772426700_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ_BEAR_1772427600_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BEAR_1772595900_1772597700</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
+  </si>
+  <si>
+    <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BEAR_1772701200_1772770500</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:15</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BULL_1772698500_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:15</t>
+  </si>
+  <si>
+    <t>Checked 3 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1772701200_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:45</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1772778600_1772786700</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772789400</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 51W / 99L / 7 OPEN  |  Win Rate: 34.0%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 150 of 157</t>
+    <t>NSE:IREDA-EQ_BULL_1772772300_1772789400</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1772790300</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:15</t>
+  </si>
+  <si>
+    <t>Entry candle not yet available — trade not entered</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1772772300_1772790300</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:30</t>
+  </si>
+  <si>
+    <t>SUMMARY — 87W / 179L / 11 OPEN  |  Win Rate: 32.7%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 266 of 277</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:R280"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5633,57 +6311,67 @@
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="3">
         <v>1397.6</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="3">
         <v>1380.2</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="3">
         <v>1396.5</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="3">
         <v>1396.4</v>
       </c>
-      <c r="I71" s="13">
+      <c r="I71" s="3">
         <v>1380.2</v>
       </c>
-      <c r="J71" s="13">
+      <c r="J71" s="3">
         <v>1412.6</v>
       </c>
-      <c r="K71" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L71" s="12" t="s">
+      <c r="K71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12"/>
-      <c r="O71" s="12"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="12" t="s">
-        <v>208</v>
+      <c r="N71" s="3">
+        <v>1380.2</v>
+      </c>
+      <c r="O71" s="2">
+        <v>124</v>
+      </c>
+      <c r="P71" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>20</v>
@@ -5716,7 +6404,7 @@
         <v>33</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N72" s="7">
         <v>1042.05</v>
@@ -5736,10 +6424,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>20</v>
@@ -5772,7 +6460,7 @@
         <v>33</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N73" s="7">
         <v>176.77</v>
@@ -5792,10 +6480,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>20</v>
@@ -5828,7 +6516,7 @@
         <v>33</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N74" s="7">
         <v>24475</v>
@@ -5848,10 +6536,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>20</v>
@@ -5884,7 +6572,7 @@
         <v>23</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N75" s="3">
         <v>1219.1</v>
@@ -5904,7 +6592,7 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>116</v>
@@ -5940,7 +6628,7 @@
         <v>23</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N76" s="3">
         <v>492.05</v>
@@ -5960,10 +6648,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>20</v>
@@ -5996,7 +6684,7 @@
         <v>23</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N77" s="3">
         <v>298.4</v>
@@ -6016,10 +6704,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>20</v>
@@ -6052,7 +6740,7 @@
         <v>33</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N78" s="7">
         <v>1324.1</v>
@@ -6072,10 +6760,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>20</v>
@@ -6108,7 +6796,7 @@
         <v>33</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N79" s="7">
         <v>316.1</v>
@@ -6128,10 +6816,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>20</v>
@@ -6164,7 +6852,7 @@
         <v>23</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N80" s="3">
         <v>2072.2</v>
@@ -6184,10 +6872,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>20</v>
@@ -6239,49 +6927,59 @@
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="C82" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" s="7">
+        <v>295.1</v>
+      </c>
+      <c r="F82" s="7">
+        <v>288</v>
+      </c>
+      <c r="G82" s="7">
+        <v>294.5</v>
+      </c>
+      <c r="H82" s="7">
+        <v>294.6</v>
+      </c>
+      <c r="I82" s="7">
+        <v>288</v>
+      </c>
+      <c r="J82" s="7">
+        <v>301.2</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M82" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E82" s="13">
-        <v>295.1</v>
-      </c>
-      <c r="F82" s="13">
-        <v>288</v>
-      </c>
-      <c r="G82" s="13">
-        <v>294.5</v>
-      </c>
-      <c r="H82" s="13">
-        <v>294.6</v>
-      </c>
-      <c r="I82" s="13">
-        <v>288</v>
-      </c>
-      <c r="J82" s="13">
+      <c r="N82" s="7">
         <v>301.2</v>
       </c>
-      <c r="K82" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L82" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12" t="s">
-        <v>208</v>
+      <c r="O82" s="6">
+        <v>75</v>
+      </c>
+      <c r="P82" s="8">
+        <v>6.6</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>2.24</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -6322,7 +7020,7 @@
         <v>23</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N83" s="3">
         <v>921.75</v>
@@ -6631,7 +7329,7 @@
         <v>64</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E89" s="3">
         <v>1160.4</v>
@@ -6793,13 +7491,13 @@
         <v>262</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E92" s="3">
         <v>1046</v>
@@ -6855,7 +7553,7 @@
         <v>20</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E93" s="3">
         <v>303.9</v>
@@ -7409,7 +8107,7 @@
         <v>288</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>20</v>
@@ -7554,7 +8252,7 @@
         <v>23</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N105" s="3">
         <v>341.65</v>
@@ -7610,7 +8308,7 @@
         <v>23</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N106" s="3">
         <v>1248.3</v>
@@ -7666,7 +8364,7 @@
         <v>23</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N107" s="3">
         <v>6230</v>
@@ -7722,7 +8420,7 @@
         <v>23</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N108" s="3">
         <v>322.65</v>
@@ -7890,7 +8588,7 @@
         <v>23</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N111" s="3">
         <v>769.55</v>
@@ -8697,7 +9395,7 @@
         <v>338</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>20</v>
@@ -8730,7 +9428,7 @@
         <v>33</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N126" s="7">
         <v>1245.2</v>
@@ -8786,7 +9484,7 @@
         <v>33</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N127" s="7">
         <v>1261.9</v>
@@ -8842,7 +9540,7 @@
         <v>33</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N128" s="7">
         <v>535.1</v>
@@ -8954,7 +9652,7 @@
         <v>33</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N130" s="7">
         <v>6191</v>
@@ -9010,7 +9708,7 @@
         <v>33</v>
       </c>
       <c r="M131" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N131" s="7">
         <v>438.7</v>
@@ -9145,13 +9843,13 @@
         <v>350</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E134" s="7">
         <v>1249.9</v>
@@ -9207,7 +9905,7 @@
         <v>20</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E135" s="7">
         <v>1270.1</v>
@@ -9263,7 +9961,7 @@
         <v>20</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E136" s="7">
         <v>312.75</v>
@@ -9275,13 +9973,13 @@
         <v>311.6</v>
       </c>
       <c r="H136" s="7">
-        <v>311.75</v>
+        <v>311.6</v>
       </c>
       <c r="I136" s="7">
         <v>307.65</v>
       </c>
       <c r="J136" s="7">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>22</v>
@@ -9293,16 +9991,16 @@
         <v>356</v>
       </c>
       <c r="N136" s="7">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="O136" s="6">
         <v>7</v>
       </c>
       <c r="P136" s="8">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q136" s="9">
-        <v>1.315</v>
+        <v>1.268</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>25</v>
@@ -9319,7 +10017,7 @@
         <v>20</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E137" s="3">
         <v>425.25</v>
@@ -9375,7 +10073,7 @@
         <v>20</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E138" s="7">
         <v>212.1</v>
@@ -9667,7 +10365,7 @@
         <v>609.4</v>
       </c>
       <c r="H143" s="3">
-        <v>609.2</v>
+        <v>609.4</v>
       </c>
       <c r="I143" s="3">
         <v>607.75</v>
@@ -9691,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="P143" s="10">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Q143" s="11">
-        <v>0.238</v>
+        <v>0.271</v>
       </c>
       <c r="R143" s="2" t="s">
         <v>25</v>
@@ -10074,7 +10772,7 @@
         <v>33</v>
       </c>
       <c r="M150" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N150" s="7">
         <v>2136.3</v>
@@ -10215,7 +10913,7 @@
         <v>20</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E153" s="7">
         <v>1213.8</v>
@@ -10261,244 +10959,6896 @@
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A154" s="12" t="s">
+      <c r="A154" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B154" s="12" t="s">
+      <c r="B154" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C154" s="12" t="s">
+      <c r="C154" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E154" s="13">
+      <c r="E154" s="3">
         <v>1687.5</v>
       </c>
-      <c r="F154" s="13">
+      <c r="F154" s="3">
         <v>1677.5</v>
       </c>
-      <c r="G154" s="13">
+      <c r="G154" s="3">
         <v>1685.9</v>
       </c>
-      <c r="H154" s="13">
+      <c r="H154" s="3">
         <v>1686.5</v>
       </c>
-      <c r="I154" s="13">
+      <c r="I154" s="3">
         <v>1677.5</v>
       </c>
-      <c r="J154" s="13">
+      <c r="J154" s="3">
         <v>1695.5</v>
       </c>
-      <c r="K154" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L154" s="12" t="s">
+      <c r="K154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N154" s="3">
+        <v>1677.5</v>
+      </c>
+      <c r="O154" s="2">
+        <v>1</v>
+      </c>
+      <c r="P154" s="4">
+        <v>-9</v>
+      </c>
+      <c r="Q154" s="5">
+        <v>-0.534</v>
+      </c>
+      <c r="R154" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E155" s="7">
+        <v>2088.9</v>
+      </c>
+      <c r="F155" s="7">
+        <v>2079.2</v>
+      </c>
+      <c r="G155" s="7">
+        <v>2086.7</v>
+      </c>
+      <c r="H155" s="7">
+        <v>2086.7</v>
+      </c>
+      <c r="I155" s="7">
+        <v>2079.2</v>
+      </c>
+      <c r="J155" s="7">
+        <v>2094.2</v>
+      </c>
+      <c r="K155" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L155" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M155" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="N155" s="7">
+        <v>2094.2</v>
+      </c>
+      <c r="O155" s="6">
+        <v>1</v>
+      </c>
+      <c r="P155" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="Q155" s="9">
+        <v>0.359</v>
+      </c>
+      <c r="R155" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E156" s="3">
+        <v>510.4</v>
+      </c>
+      <c r="F156" s="3">
+        <v>506.15</v>
+      </c>
+      <c r="G156" s="3">
+        <v>509.4</v>
+      </c>
+      <c r="H156" s="3">
+        <v>509.4</v>
+      </c>
+      <c r="I156" s="3">
+        <v>506.15</v>
+      </c>
+      <c r="J156" s="3">
+        <v>512.65</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N156" s="3">
+        <v>506.15</v>
+      </c>
+      <c r="O156" s="2">
+        <v>1</v>
+      </c>
+      <c r="P156" s="4">
+        <v>-3.25</v>
+      </c>
+      <c r="Q156" s="5">
+        <v>-0.638</v>
+      </c>
+      <c r="R156" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E157" s="7">
+        <v>624.1</v>
+      </c>
+      <c r="F157" s="7">
+        <v>618.45</v>
+      </c>
+      <c r="G157" s="7">
+        <v>624</v>
+      </c>
+      <c r="H157" s="7">
+        <v>624.1</v>
+      </c>
+      <c r="I157" s="7">
+        <v>618.45</v>
+      </c>
+      <c r="J157" s="7">
+        <v>629.75</v>
+      </c>
+      <c r="K157" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L157" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M157" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="N157" s="7">
+        <v>629.75</v>
+      </c>
+      <c r="O157" s="6">
+        <v>2</v>
+      </c>
+      <c r="P157" s="8">
+        <v>5.65</v>
+      </c>
+      <c r="Q157" s="9">
+        <v>0.905</v>
+      </c>
+      <c r="R157" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E158" s="3">
+        <v>542.7</v>
+      </c>
+      <c r="F158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="G158" s="3">
+        <v>541.25</v>
+      </c>
+      <c r="H158" s="3">
+        <v>541.55</v>
+      </c>
+      <c r="I158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="J158" s="3">
+        <v>543.05</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="O158" s="2">
+        <v>1</v>
+      </c>
+      <c r="P158" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="Q158" s="5">
+        <v>-0.277</v>
+      </c>
+      <c r="R158" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E159" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="F159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="G159" s="3">
+        <v>620</v>
+      </c>
+      <c r="H159" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="I159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="J159" s="3">
+        <v>624.75</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="N159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="O159" s="2">
+        <v>3</v>
+      </c>
+      <c r="P159" s="4">
+        <v>-4.25</v>
+      </c>
+      <c r="Q159" s="5">
+        <v>-0.685</v>
+      </c>
+      <c r="R159" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E160" s="7">
+        <v>2164.5</v>
+      </c>
+      <c r="F160" s="7">
+        <v>2139</v>
+      </c>
+      <c r="G160" s="7">
+        <v>2159.3</v>
+      </c>
+      <c r="H160" s="7">
+        <v>2158.6</v>
+      </c>
+      <c r="I160" s="7">
+        <v>2139</v>
+      </c>
+      <c r="J160" s="7">
+        <v>2178.2</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L160" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M160" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="N160" s="7">
+        <v>2178.2</v>
+      </c>
+      <c r="O160" s="6">
+        <v>2</v>
+      </c>
+      <c r="P160" s="8">
+        <v>19.6</v>
+      </c>
+      <c r="Q160" s="9">
+        <v>0.908</v>
+      </c>
+      <c r="R160" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E161" s="3">
+        <v>2247.7</v>
+      </c>
+      <c r="F161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="G161" s="3">
+        <v>2242.4</v>
+      </c>
+      <c r="H161" s="3">
+        <v>2242.4</v>
+      </c>
+      <c r="I161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="J161" s="3">
+        <v>2250.5</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="N161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="O161" s="2">
+        <v>1</v>
+      </c>
+      <c r="P161" s="4">
+        <v>-8.1</v>
+      </c>
+      <c r="Q161" s="5">
+        <v>-0.361</v>
+      </c>
+      <c r="R161" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E162" s="3">
+        <v>982.9</v>
+      </c>
+      <c r="F162" s="3">
+        <v>973</v>
+      </c>
+      <c r="G162" s="3">
+        <v>976.45</v>
+      </c>
+      <c r="H162" s="3">
+        <v>976.5</v>
+      </c>
+      <c r="I162" s="3">
+        <v>973</v>
+      </c>
+      <c r="J162" s="3">
+        <v>973</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="N162" s="3">
+        <v>973</v>
+      </c>
+      <c r="O162" s="2">
+        <v>1</v>
+      </c>
+      <c r="P162" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="Q162" s="11">
+        <v>0.358</v>
+      </c>
+      <c r="R162" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E163" s="7">
+        <v>6468</v>
+      </c>
+      <c r="F163" s="7">
+        <v>6420</v>
+      </c>
+      <c r="G163" s="7">
+        <v>6466</v>
+      </c>
+      <c r="H163" s="7">
+        <v>6465</v>
+      </c>
+      <c r="I163" s="7">
+        <v>6420</v>
+      </c>
+      <c r="J163" s="7">
+        <v>6510</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L163" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M163" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="N163" s="7">
+        <v>6510</v>
+      </c>
+      <c r="O163" s="6">
+        <v>1</v>
+      </c>
+      <c r="P163" s="8">
+        <v>45</v>
+      </c>
+      <c r="Q163" s="9">
+        <v>0.696</v>
+      </c>
+      <c r="R163" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E164" s="7">
+        <v>948</v>
+      </c>
+      <c r="F164" s="7">
+        <v>935.15</v>
+      </c>
+      <c r="G164" s="7">
+        <v>947.55</v>
+      </c>
+      <c r="H164" s="7">
+        <v>947.25</v>
+      </c>
+      <c r="I164" s="7">
+        <v>935.15</v>
+      </c>
+      <c r="J164" s="7">
+        <v>959.35</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L164" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M164" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="N164" s="7">
+        <v>959.35</v>
+      </c>
+      <c r="O164" s="6">
+        <v>1</v>
+      </c>
+      <c r="P164" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="Q164" s="9">
+        <v>1.277</v>
+      </c>
+      <c r="R164" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E165" s="3">
+        <v>171.2</v>
+      </c>
+      <c r="F165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="G165" s="3">
+        <v>170.66</v>
+      </c>
+      <c r="H165" s="3">
+        <v>170.6</v>
+      </c>
+      <c r="I165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="J165" s="3">
+        <v>170.9</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="N165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="O165" s="2">
+        <v>1</v>
+      </c>
+      <c r="P165" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="Q165" s="5">
+        <v>-0.176</v>
+      </c>
+      <c r="R165" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E166" s="3">
+        <v>130.7</v>
+      </c>
+      <c r="F166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="G166" s="3">
+        <v>129.65</v>
+      </c>
+      <c r="H166" s="3">
+        <v>129.66</v>
+      </c>
+      <c r="I166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="J166" s="3">
+        <v>130.71</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="N166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="O166" s="2">
+        <v>2</v>
+      </c>
+      <c r="P166" s="4">
+        <v>-1.05</v>
+      </c>
+      <c r="Q166" s="5">
+        <v>-0.81</v>
+      </c>
+      <c r="R166" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E167" s="7">
+        <v>946.8</v>
+      </c>
+      <c r="F167" s="7">
+        <v>936.3</v>
+      </c>
+      <c r="G167" s="7">
+        <v>945.95</v>
+      </c>
+      <c r="H167" s="7">
+        <v>945.95</v>
+      </c>
+      <c r="I167" s="7">
+        <v>936.3</v>
+      </c>
+      <c r="J167" s="7">
+        <v>955.6</v>
+      </c>
+      <c r="K167" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L167" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M167" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="N167" s="7">
+        <v>955.6</v>
+      </c>
+      <c r="O167" s="6">
+        <v>1</v>
+      </c>
+      <c r="P167" s="8">
+        <v>9.65</v>
+      </c>
+      <c r="Q167" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="R167" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E168" s="3">
+        <v>3987.9</v>
+      </c>
+      <c r="F168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="G168" s="3">
+        <v>3966.1</v>
+      </c>
+      <c r="H168" s="3">
+        <v>3964.8</v>
+      </c>
+      <c r="I168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="J168" s="3">
+        <v>4013.6</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="O168" s="2">
+        <v>12</v>
+      </c>
+      <c r="P168" s="4">
+        <v>-48.8</v>
+      </c>
+      <c r="Q168" s="5">
+        <v>-1.231</v>
+      </c>
+      <c r="R168" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E169" s="3">
+        <v>154.34</v>
+      </c>
+      <c r="F169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="G169" s="3">
+        <v>153.52</v>
+      </c>
+      <c r="H169" s="3">
+        <v>153.6</v>
+      </c>
+      <c r="I169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="J169" s="3">
+        <v>155.98</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="N169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="O169" s="2">
+        <v>30</v>
+      </c>
+      <c r="P169" s="4">
+        <v>-2.38</v>
+      </c>
+      <c r="Q169" s="5">
+        <v>-1.549</v>
+      </c>
+      <c r="R169" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E170" s="3">
+        <v>869.15</v>
+      </c>
+      <c r="F170" s="3">
+        <v>836.05</v>
+      </c>
+      <c r="G170" s="3">
+        <v>855</v>
+      </c>
+      <c r="H170" s="3">
+        <v>855</v>
+      </c>
+      <c r="I170" s="3">
+        <v>836.05</v>
+      </c>
+      <c r="J170" s="3">
+        <v>873.95</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N170" s="3">
+        <v>836.05</v>
+      </c>
+      <c r="O170" s="2">
+        <v>26</v>
+      </c>
+      <c r="P170" s="4">
+        <v>-18.95</v>
+      </c>
+      <c r="Q170" s="5">
+        <v>-2.216</v>
+      </c>
+      <c r="R170" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E171" s="3">
+        <v>1105</v>
+      </c>
+      <c r="F171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="G171" s="3">
+        <v>1099.3</v>
+      </c>
+      <c r="H171" s="3">
+        <v>1099.4</v>
+      </c>
+      <c r="I171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="J171" s="3">
+        <v>1111.8</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="O171" s="2">
+        <v>11</v>
+      </c>
+      <c r="P171" s="4">
+        <v>-12.4</v>
+      </c>
+      <c r="Q171" s="5">
+        <v>-1.128</v>
+      </c>
+      <c r="R171" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E172" s="7">
+        <v>2793.6</v>
+      </c>
+      <c r="F172" s="7">
+        <v>2770</v>
+      </c>
+      <c r="G172" s="7">
+        <v>2791.2</v>
+      </c>
+      <c r="H172" s="7">
+        <v>2791.4</v>
+      </c>
+      <c r="I172" s="7">
+        <v>2770</v>
+      </c>
+      <c r="J172" s="7">
+        <v>2812.8</v>
+      </c>
+      <c r="K172" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M172" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="N172" s="7">
+        <v>2812.8</v>
+      </c>
+      <c r="O172" s="6">
+        <v>2</v>
+      </c>
+      <c r="P172" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="Q172" s="9">
+        <v>0.767</v>
+      </c>
+      <c r="R172" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E173" s="3">
+        <v>630.75</v>
+      </c>
+      <c r="F173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="G173" s="3">
+        <v>628.55</v>
+      </c>
+      <c r="H173" s="3">
+        <v>628.5</v>
+      </c>
+      <c r="I173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="J173" s="3">
+        <v>636.5</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="O173" s="2">
+        <v>11</v>
+      </c>
+      <c r="P173" s="4">
+        <v>-8</v>
+      </c>
+      <c r="Q173" s="5">
+        <v>-1.273</v>
+      </c>
+      <c r="R173" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E174" s="3">
+        <v>1364.6</v>
+      </c>
+      <c r="F174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="G174" s="3">
+        <v>1363.9</v>
+      </c>
+      <c r="H174" s="3">
+        <v>1363.5</v>
+      </c>
+      <c r="I174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="J174" s="3">
+        <v>1373.9</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="O174" s="2">
+        <v>1</v>
+      </c>
+      <c r="P174" s="4">
+        <v>-10.4</v>
+      </c>
+      <c r="Q174" s="5">
+        <v>-0.763</v>
+      </c>
+      <c r="R174" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E175" s="3">
+        <v>500.35</v>
+      </c>
+      <c r="F175" s="3">
+        <v>493.9</v>
+      </c>
+      <c r="G175" s="3">
+        <v>500.3</v>
+      </c>
+      <c r="H175" s="3">
+        <v>500.2</v>
+      </c>
+      <c r="I175" s="3">
+        <v>493.9</v>
+      </c>
+      <c r="J175" s="3">
+        <v>506.5</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N175" s="3">
+        <v>493.9</v>
+      </c>
+      <c r="O175" s="2">
+        <v>22</v>
+      </c>
+      <c r="P175" s="4">
+        <v>-6.3</v>
+      </c>
+      <c r="Q175" s="5">
+        <v>-1.259</v>
+      </c>
+      <c r="R175" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E176" s="3">
+        <v>13770</v>
+      </c>
+      <c r="F176" s="3">
+        <v>13554</v>
+      </c>
+      <c r="G176" s="3">
+        <v>13741</v>
+      </c>
+      <c r="H176" s="3">
+        <v>13740</v>
+      </c>
+      <c r="I176" s="3">
+        <v>13554</v>
+      </c>
+      <c r="J176" s="3">
+        <v>13926</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N176" s="3">
+        <v>13554</v>
+      </c>
+      <c r="O176" s="2">
+        <v>22</v>
+      </c>
+      <c r="P176" s="4">
+        <v>-186</v>
+      </c>
+      <c r="Q176" s="5">
+        <v>-1.354</v>
+      </c>
+      <c r="R176" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E177" s="7">
+        <v>390.45</v>
+      </c>
+      <c r="F177" s="7">
+        <v>386.6</v>
+      </c>
+      <c r="G177" s="7">
+        <v>389.65</v>
+      </c>
+      <c r="H177" s="7">
+        <v>389.75</v>
+      </c>
+      <c r="I177" s="7">
+        <v>386.6</v>
+      </c>
+      <c r="J177" s="7">
+        <v>392.9</v>
+      </c>
+      <c r="K177" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L177" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M177" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="N177" s="7">
+        <v>392.9</v>
+      </c>
+      <c r="O177" s="6">
+        <v>19</v>
+      </c>
+      <c r="P177" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="Q177" s="9">
+        <v>0.808</v>
+      </c>
+      <c r="R177" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E178" s="3">
+        <v>385.4</v>
+      </c>
+      <c r="F178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="G178" s="3">
+        <v>383.3</v>
+      </c>
+      <c r="H178" s="3">
+        <v>383.5</v>
+      </c>
+      <c r="I178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="J178" s="3">
+        <v>385.55</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="N178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="O178" s="2">
+        <v>3</v>
+      </c>
+      <c r="P178" s="4">
+        <v>-2.05</v>
+      </c>
+      <c r="Q178" s="5">
+        <v>-0.535</v>
+      </c>
+      <c r="R178" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E179" s="3">
+        <v>2054.9</v>
+      </c>
+      <c r="F179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2050.4</v>
+      </c>
+      <c r="H179" s="3">
+        <v>2050.5</v>
+      </c>
+      <c r="I179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="J179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="O179" s="2">
+        <v>1</v>
+      </c>
+      <c r="P179" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="Q179" s="11">
+        <v>0.166</v>
+      </c>
+      <c r="R179" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E180" s="7">
+        <v>1100.05</v>
+      </c>
+      <c r="F180" s="7">
+        <v>1089</v>
+      </c>
+      <c r="G180" s="7">
+        <v>1100.05</v>
+      </c>
+      <c r="H180" s="7">
+        <v>1100.35</v>
+      </c>
+      <c r="I180" s="7">
+        <v>1089</v>
+      </c>
+      <c r="J180" s="7">
+        <v>1111.7</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L180" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M180" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="N180" s="7">
+        <v>1111.7</v>
+      </c>
+      <c r="O180" s="6">
+        <v>13</v>
+      </c>
+      <c r="P180" s="8">
+        <v>11.35</v>
+      </c>
+      <c r="Q180" s="9">
+        <v>1.031</v>
+      </c>
+      <c r="R180" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="E181" s="7">
+        <v>1020.15</v>
+      </c>
+      <c r="F181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="G181" s="7">
+        <v>1015.1</v>
+      </c>
+      <c r="H181" s="7">
+        <v>1015.05</v>
+      </c>
+      <c r="I181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="J181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="K181" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L181" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M181" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="N181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="O181" s="6">
+        <v>1</v>
+      </c>
+      <c r="P181" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="Q181" s="9">
+        <v>0.286</v>
+      </c>
+      <c r="R181" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E182" s="3">
+        <v>15208</v>
+      </c>
+      <c r="F182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="G182" s="3">
+        <v>15195</v>
+      </c>
+      <c r="H182" s="3">
+        <v>15191</v>
+      </c>
+      <c r="I182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="J182" s="3">
+        <v>15232</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="N182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="O182" s="2">
+        <v>3</v>
+      </c>
+      <c r="P182" s="4">
+        <v>-41</v>
+      </c>
+      <c r="Q182" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="R182" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A183" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E183" s="7">
+        <v>424.6</v>
+      </c>
+      <c r="F183" s="7">
+        <v>423</v>
+      </c>
+      <c r="G183" s="7">
+        <v>423.15</v>
+      </c>
+      <c r="H183" s="7">
+        <v>423.15</v>
+      </c>
+      <c r="I183" s="7">
+        <v>423</v>
+      </c>
+      <c r="J183" s="7">
+        <v>423</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L183" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M183" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="N183" s="7">
+        <v>423</v>
+      </c>
+      <c r="O183" s="6">
+        <v>1</v>
+      </c>
+      <c r="P183" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="Q183" s="9">
+        <v>0.035</v>
+      </c>
+      <c r="R183" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E184" s="7">
+        <v>447.35</v>
+      </c>
+      <c r="F184" s="7">
+        <v>445.4</v>
+      </c>
+      <c r="G184" s="7">
+        <v>447.3</v>
+      </c>
+      <c r="H184" s="7">
+        <v>447.3</v>
+      </c>
+      <c r="I184" s="7">
+        <v>445.4</v>
+      </c>
+      <c r="J184" s="7">
+        <v>449.2</v>
+      </c>
+      <c r="K184" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L184" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M184" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="N184" s="7">
+        <v>449.2</v>
+      </c>
+      <c r="O184" s="6">
+        <v>1</v>
+      </c>
+      <c r="P184" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="Q184" s="9">
+        <v>0.425</v>
+      </c>
+      <c r="R184" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E185" s="3">
+        <v>964.9</v>
+      </c>
+      <c r="F185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="G185" s="3">
+        <v>963.65</v>
+      </c>
+      <c r="H185" s="3">
+        <v>963.95</v>
+      </c>
+      <c r="I185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="J185" s="3">
+        <v>970.65</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="O185" s="2">
+        <v>1</v>
+      </c>
+      <c r="P185" s="4">
+        <v>-6.7</v>
+      </c>
+      <c r="Q185" s="5">
+        <v>-0.695</v>
+      </c>
+      <c r="R185" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E186" s="3">
+        <v>2284</v>
+      </c>
+      <c r="F186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="G186" s="3">
+        <v>2282.5</v>
+      </c>
+      <c r="H186" s="3">
+        <v>2282.6</v>
+      </c>
+      <c r="I186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="J186" s="3">
+        <v>2294.2</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="O186" s="2">
+        <v>1</v>
+      </c>
+      <c r="P186" s="4">
+        <v>-11.6</v>
+      </c>
+      <c r="Q186" s="5">
+        <v>-0.508</v>
+      </c>
+      <c r="R186" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E187" s="3">
+        <v>135.65</v>
+      </c>
+      <c r="F187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="G187" s="3">
+        <v>135.35</v>
+      </c>
+      <c r="H187" s="3">
+        <v>135.33</v>
+      </c>
+      <c r="I187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="J187" s="3">
+        <v>135.71</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="O187" s="2">
+        <v>1</v>
+      </c>
+      <c r="P187" s="4">
+        <v>-0.38</v>
+      </c>
+      <c r="Q187" s="5">
+        <v>-0.281</v>
+      </c>
+      <c r="R187" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E188" s="3">
+        <v>546</v>
+      </c>
+      <c r="F188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="G188" s="3">
+        <v>545.3</v>
+      </c>
+      <c r="H188" s="3">
+        <v>545.3</v>
+      </c>
+      <c r="I188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="J188" s="3">
+        <v>547.45</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="O188" s="2">
+        <v>1</v>
+      </c>
+      <c r="P188" s="4">
+        <v>-2.15</v>
+      </c>
+      <c r="Q188" s="5">
+        <v>-0.394</v>
+      </c>
+      <c r="R188" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E189" s="3">
+        <v>391.8</v>
+      </c>
+      <c r="F189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="G189" s="3">
+        <v>391.65</v>
+      </c>
+      <c r="H189" s="3">
+        <v>391.7</v>
+      </c>
+      <c r="I189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="J189" s="3">
+        <v>394.5</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="O189" s="2">
+        <v>2</v>
+      </c>
+      <c r="P189" s="4">
+        <v>-2.8</v>
+      </c>
+      <c r="Q189" s="5">
+        <v>-0.715</v>
+      </c>
+      <c r="R189" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E190" s="3">
+        <v>6880</v>
+      </c>
+      <c r="F190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="G190" s="3">
+        <v>6870</v>
+      </c>
+      <c r="H190" s="3">
+        <v>6904</v>
+      </c>
+      <c r="I190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="J190" s="3">
+        <v>6967.5</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="O190" s="2">
+        <v>3</v>
+      </c>
+      <c r="P190" s="4">
+        <v>-63.5</v>
+      </c>
+      <c r="Q190" s="5">
+        <v>-0.92</v>
+      </c>
+      <c r="R190" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E191" s="3">
+        <v>130.72</v>
+      </c>
+      <c r="F191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="G191" s="3">
+        <v>130.14</v>
+      </c>
+      <c r="H191" s="3">
+        <v>130.25</v>
+      </c>
+      <c r="I191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="J191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="O191" s="2">
+        <v>1</v>
+      </c>
+      <c r="P191" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="Q191" s="11">
+        <v>0.092</v>
+      </c>
+      <c r="R191" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E192" s="3">
+        <v>3970</v>
+      </c>
+      <c r="F192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="G192" s="3">
+        <v>3959.9</v>
+      </c>
+      <c r="H192" s="3">
+        <v>3954.2</v>
+      </c>
+      <c r="I192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="J192" s="3">
+        <v>3956.6</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="O192" s="2">
+        <v>1</v>
+      </c>
+      <c r="P192" s="4">
+        <v>-2.4</v>
+      </c>
+      <c r="Q192" s="5">
+        <v>-0.061</v>
+      </c>
+      <c r="R192" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E193" s="3">
+        <v>2241.8</v>
+      </c>
+      <c r="F193" s="3">
+        <v>2224.4</v>
+      </c>
+      <c r="G193" s="3">
+        <v>2238</v>
+      </c>
+      <c r="H193" s="3">
+        <v>2238</v>
+      </c>
+      <c r="I193" s="3">
+        <v>2224.4</v>
+      </c>
+      <c r="J193" s="3">
+        <v>2251.6</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N193" s="3">
+        <v>2224.4</v>
+      </c>
+      <c r="O193" s="2">
+        <v>2</v>
+      </c>
+      <c r="P193" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="Q193" s="5">
+        <v>-0.608</v>
+      </c>
+      <c r="R193" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E194" s="3">
+        <v>6142.5</v>
+      </c>
+      <c r="F194" s="3">
+        <v>6065.5</v>
+      </c>
+      <c r="G194" s="3">
+        <v>6065.5</v>
+      </c>
+      <c r="H194" s="3">
+        <v>6067</v>
+      </c>
+      <c r="I194" s="3">
+        <v>6065.5</v>
+      </c>
+      <c r="J194" s="3">
+        <v>6065.5</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N194" s="3">
+        <v>6065.5</v>
+      </c>
+      <c r="O194" s="2">
+        <v>1</v>
+      </c>
+      <c r="P194" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="Q194" s="11">
+        <v>0.025</v>
+      </c>
+      <c r="R194" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E195" s="3">
+        <v>504.9</v>
+      </c>
+      <c r="F195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="G195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="H195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="I195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="J195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="O195" s="2">
+        <v>1</v>
+      </c>
+      <c r="P195" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="11">
+        <v>0</v>
+      </c>
+      <c r="R195" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E196" s="3">
+        <v>297.5</v>
+      </c>
+      <c r="F196" s="3">
+        <v>278</v>
+      </c>
+      <c r="G196" s="3">
+        <v>289.6</v>
+      </c>
+      <c r="H196" s="3">
+        <v>289.6</v>
+      </c>
+      <c r="I196" s="3">
+        <v>278</v>
+      </c>
+      <c r="J196" s="3">
+        <v>278</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N196" s="3">
+        <v>278</v>
+      </c>
+      <c r="O196" s="2">
+        <v>1</v>
+      </c>
+      <c r="P196" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="Q196" s="11">
+        <v>4.006</v>
+      </c>
+      <c r="R196" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E197" s="3">
+        <v>1854.6</v>
+      </c>
+      <c r="F197" s="3">
+        <v>1840</v>
+      </c>
+      <c r="G197" s="3">
+        <v>1841.7</v>
+      </c>
+      <c r="H197" s="3">
+        <v>1841.4</v>
+      </c>
+      <c r="I197" s="3">
+        <v>1840</v>
+      </c>
+      <c r="J197" s="3">
+        <v>1840</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N197" s="3">
+        <v>1840</v>
+      </c>
+      <c r="O197" s="2">
+        <v>1</v>
+      </c>
+      <c r="P197" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="Q197" s="11">
+        <v>0.076</v>
+      </c>
+      <c r="R197" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A198" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E198" s="7">
+        <v>3458</v>
+      </c>
+      <c r="F198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="G198" s="7">
+        <v>3408</v>
+      </c>
+      <c r="H198" s="7">
+        <v>3408</v>
+      </c>
+      <c r="I198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="J198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M198" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="O198" s="6">
+        <v>1</v>
+      </c>
+      <c r="P198" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="Q198" s="9">
+        <v>0.349</v>
+      </c>
+      <c r="R198" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A199" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E199" s="7">
+        <v>162.4</v>
+      </c>
+      <c r="F199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="G199" s="7">
+        <v>160.78</v>
+      </c>
+      <c r="H199" s="7">
+        <v>160.78</v>
+      </c>
+      <c r="I199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="J199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="K199" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M199" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="O199" s="6">
+        <v>1</v>
+      </c>
+      <c r="P199" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="Q199" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="R199" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A200" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E200" s="7">
+        <v>12897</v>
+      </c>
+      <c r="F200" s="7">
+        <v>12763</v>
+      </c>
+      <c r="G200" s="7">
+        <v>12806</v>
+      </c>
+      <c r="H200" s="7">
+        <v>12808</v>
+      </c>
+      <c r="I200" s="7">
+        <v>12763</v>
+      </c>
+      <c r="J200" s="7">
+        <v>12763</v>
+      </c>
+      <c r="K200" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M200" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N200" s="7">
+        <v>12763</v>
+      </c>
+      <c r="O200" s="6">
+        <v>1</v>
+      </c>
+      <c r="P200" s="8">
+        <v>45</v>
+      </c>
+      <c r="Q200" s="9">
+        <v>0.351</v>
+      </c>
+      <c r="R200" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A201" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E201" s="7">
+        <v>1555.5</v>
+      </c>
+      <c r="F201" s="7">
+        <v>1534.2</v>
+      </c>
+      <c r="G201" s="7">
+        <v>1553.3</v>
+      </c>
+      <c r="H201" s="7">
+        <v>1553.7</v>
+      </c>
+      <c r="I201" s="7">
+        <v>1534.2</v>
+      </c>
+      <c r="J201" s="7">
+        <v>1573.2</v>
+      </c>
+      <c r="K201" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M201" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="N201" s="7">
+        <v>1573.2</v>
+      </c>
+      <c r="O201" s="6">
+        <v>7</v>
+      </c>
+      <c r="P201" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="Q201" s="9">
+        <v>1.255</v>
+      </c>
+      <c r="R201" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A202" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E202" s="7">
+        <v>21.01</v>
+      </c>
+      <c r="F202" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="G202" s="7">
+        <v>20.81</v>
+      </c>
+      <c r="H202" s="7">
+        <v>20.82</v>
+      </c>
+      <c r="I202" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="J202" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="K202" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L202" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M202" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N202" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="O202" s="6">
+        <v>1</v>
+      </c>
+      <c r="P202" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="Q202" s="9">
+        <v>0.096</v>
+      </c>
+      <c r="R202" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A203" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E203" s="7">
+        <v>478.6</v>
+      </c>
+      <c r="F203" s="7">
+        <v>473.5</v>
+      </c>
+      <c r="G203" s="7">
+        <v>477.2</v>
+      </c>
+      <c r="H203" s="7">
+        <v>477.1</v>
+      </c>
+      <c r="I203" s="7">
+        <v>473.5</v>
+      </c>
+      <c r="J203" s="7">
+        <v>480.7</v>
+      </c>
+      <c r="K203" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L203" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M203" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="N203" s="7">
+        <v>480.7</v>
+      </c>
+      <c r="O203" s="6">
+        <v>3</v>
+      </c>
+      <c r="P203" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="Q203" s="9">
+        <v>0.755</v>
+      </c>
+      <c r="R203" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E204" s="3">
+        <v>352.7</v>
+      </c>
+      <c r="F204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="G204" s="3">
+        <v>351</v>
+      </c>
+      <c r="H204" s="3">
+        <v>350.7</v>
+      </c>
+      <c r="I204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="J204" s="3">
+        <v>350.6</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M204" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="O204" s="2">
+        <v>1</v>
+      </c>
+      <c r="P204" s="4">
+        <v>-0.1</v>
+      </c>
+      <c r="Q204" s="5">
+        <v>-0.029</v>
+      </c>
+      <c r="R204" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E205" s="3">
+        <v>69</v>
+      </c>
+      <c r="F205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="G205" s="3">
+        <v>68.77</v>
+      </c>
+      <c r="H205" s="3">
+        <v>68.77</v>
+      </c>
+      <c r="I205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="J205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M205" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="O205" s="2">
+        <v>1</v>
+      </c>
+      <c r="P205" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="Q205" s="11">
+        <v>0.029</v>
+      </c>
+      <c r="R205" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E206" s="3">
+        <v>302.8</v>
+      </c>
+      <c r="F206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="G206" s="3">
+        <v>302.05</v>
+      </c>
+      <c r="H206" s="3">
+        <v>302.05</v>
+      </c>
+      <c r="I206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="J206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="O206" s="2">
+        <v>1</v>
+      </c>
+      <c r="P206" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q206" s="11">
+        <v>0.182</v>
+      </c>
+      <c r="R206" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E207" s="3">
+        <v>2731</v>
+      </c>
+      <c r="F207" s="3">
+        <v>2717</v>
+      </c>
+      <c r="G207" s="3">
+        <v>2718.6</v>
+      </c>
+      <c r="H207" s="3">
+        <v>2718.6</v>
+      </c>
+      <c r="I207" s="3">
+        <v>2717</v>
+      </c>
+      <c r="J207" s="3">
+        <v>2717</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="N207" s="3">
+        <v>2717</v>
+      </c>
+      <c r="O207" s="2">
+        <v>1</v>
+      </c>
+      <c r="P207" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="Q207" s="11">
+        <v>0.059</v>
+      </c>
+      <c r="R207" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E208" s="3">
+        <v>429.7</v>
+      </c>
+      <c r="F208" s="3">
+        <v>426.9</v>
+      </c>
+      <c r="G208" s="3">
+        <v>426.9</v>
+      </c>
+      <c r="H208" s="3">
+        <v>427.1</v>
+      </c>
+      <c r="I208" s="3">
+        <v>426.9</v>
+      </c>
+      <c r="J208" s="3">
+        <v>426.9</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M208" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="N208" s="3">
+        <v>426.9</v>
+      </c>
+      <c r="O208" s="2">
+        <v>1</v>
+      </c>
+      <c r="P208" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Q208" s="11">
+        <v>0.047</v>
+      </c>
+      <c r="R208" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E209" s="3">
+        <v>770</v>
+      </c>
+      <c r="F209" s="3">
+        <v>768.5</v>
+      </c>
+      <c r="G209" s="3">
+        <v>768.95</v>
+      </c>
+      <c r="H209" s="3">
+        <v>768.95</v>
+      </c>
+      <c r="I209" s="3">
+        <v>768.5</v>
+      </c>
+      <c r="J209" s="3">
+        <v>768.5</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M209" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="N209" s="3">
+        <v>768.5</v>
+      </c>
+      <c r="O209" s="2">
+        <v>1</v>
+      </c>
+      <c r="P209" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="Q209" s="11">
+        <v>0.059</v>
+      </c>
+      <c r="R209" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E210" s="3">
+        <v>1228.4</v>
+      </c>
+      <c r="F210" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="G210" s="3">
+        <v>1220.9</v>
+      </c>
+      <c r="H210" s="3">
+        <v>1220.9</v>
+      </c>
+      <c r="I210" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="J210" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M210" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="N210" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="O210" s="2">
+        <v>1</v>
+      </c>
+      <c r="P210" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="Q210" s="11">
+        <v>0.049</v>
+      </c>
+      <c r="R210" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E211" s="3">
+        <v>6985</v>
+      </c>
+      <c r="F211" s="3">
+        <v>6950</v>
+      </c>
+      <c r="G211" s="3">
+        <v>6976</v>
+      </c>
+      <c r="H211" s="3">
+        <v>6976</v>
+      </c>
+      <c r="I211" s="3">
+        <v>6950</v>
+      </c>
+      <c r="J211" s="3">
+        <v>7002</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L211" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M211" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="N211" s="3">
+        <v>6950</v>
+      </c>
+      <c r="O211" s="2">
+        <v>1</v>
+      </c>
+      <c r="P211" s="4">
+        <v>-26</v>
+      </c>
+      <c r="Q211" s="5">
+        <v>-0.373</v>
+      </c>
+      <c r="R211" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A212" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E212" s="7">
+        <v>1205.8</v>
+      </c>
+      <c r="F212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="G212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="H212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="I212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="J212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="K212" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M212" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="N212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="O212" s="6">
+        <v>1</v>
+      </c>
+      <c r="P212" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q212" s="9">
+        <v>0</v>
+      </c>
+      <c r="R212" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E213" s="3">
+        <v>151.28</v>
+      </c>
+      <c r="F213" s="3">
+        <v>150.67</v>
+      </c>
+      <c r="G213" s="3">
+        <v>150.75</v>
+      </c>
+      <c r="H213" s="3">
+        <v>150.81</v>
+      </c>
+      <c r="I213" s="3">
+        <v>150.67</v>
+      </c>
+      <c r="J213" s="3">
+        <v>150.67</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L213" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M213" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="N213" s="3">
+        <v>150.67</v>
+      </c>
+      <c r="O213" s="2">
+        <v>1</v>
+      </c>
+      <c r="P213" s="10">
+        <v>0.14</v>
+      </c>
+      <c r="Q213" s="11">
+        <v>0.093</v>
+      </c>
+      <c r="R213" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E214" s="3">
+        <v>3159.3</v>
+      </c>
+      <c r="F214" s="3">
+        <v>3139.3</v>
+      </c>
+      <c r="G214" s="3">
+        <v>3159.3</v>
+      </c>
+      <c r="H214" s="3">
+        <v>3158.6</v>
+      </c>
+      <c r="I214" s="3">
+        <v>3139.3</v>
+      </c>
+      <c r="J214" s="3">
+        <v>3177.9</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M214" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="N214" s="3">
+        <v>3139.3</v>
+      </c>
+      <c r="O214" s="2">
+        <v>1</v>
+      </c>
+      <c r="P214" s="4">
+        <v>-19.3</v>
+      </c>
+      <c r="Q214" s="5">
+        <v>-0.611</v>
+      </c>
+      <c r="R214" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E215" s="3">
+        <v>347.25</v>
+      </c>
+      <c r="F215" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="G215" s="3">
+        <v>344.9</v>
+      </c>
+      <c r="H215" s="3">
+        <v>344.9</v>
+      </c>
+      <c r="I215" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="J215" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L215" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M215" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M154" s="12"/>
-      <c r="N154" s="12"/>
-      <c r="O154" s="12"/>
-      <c r="P154" s="12"/>
-      <c r="Q154" s="12"/>
-      <c r="R154" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A155" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="B155" s="12" t="s">
+      <c r="N215" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="O215" s="2">
+        <v>1</v>
+      </c>
+      <c r="P215" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="Q215" s="11">
+        <v>1.943</v>
+      </c>
+      <c r="R215" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A216" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E216" s="7">
+        <v>3866.5</v>
+      </c>
+      <c r="F216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="G216" s="7">
+        <v>3841.2</v>
+      </c>
+      <c r="H216" s="7">
+        <v>3842.1</v>
+      </c>
+      <c r="I216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="J216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="K216" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M216" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="O216" s="6">
+        <v>1</v>
+      </c>
+      <c r="P216" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="Q216" s="9">
+        <v>0.055</v>
+      </c>
+      <c r="R216" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E217" s="3">
+        <v>391.7</v>
+      </c>
+      <c r="F217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="G217" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="H217" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="I217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="J217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M217" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="O217" s="2">
+        <v>1</v>
+      </c>
+      <c r="P217" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q217" s="11">
+        <v>0.257</v>
+      </c>
+      <c r="R217" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A218" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E218" s="7">
+        <v>337.2</v>
+      </c>
+      <c r="F218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="G218" s="7">
+        <v>334</v>
+      </c>
+      <c r="H218" s="7">
+        <v>334</v>
+      </c>
+      <c r="I218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="J218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="K218" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M218" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="O218" s="6">
+        <v>1</v>
+      </c>
+      <c r="P218" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q218" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="R218" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A219" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E219" s="7">
+        <v>1415.8</v>
+      </c>
+      <c r="F219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="G219" s="7">
+        <v>1397</v>
+      </c>
+      <c r="H219" s="7">
+        <v>1396.7</v>
+      </c>
+      <c r="I219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="J219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="K219" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M219" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="O219" s="6">
+        <v>1</v>
+      </c>
+      <c r="P219" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="Q219" s="9">
+        <v>0.093</v>
+      </c>
+      <c r="R219" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E220" s="3">
+        <v>2349.3</v>
+      </c>
+      <c r="F220" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="G220" s="3">
+        <v>2339.5</v>
+      </c>
+      <c r="H220" s="3">
+        <v>2339.4</v>
+      </c>
+      <c r="I220" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="J220" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N220" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="O220" s="2">
+        <v>1</v>
+      </c>
+      <c r="P220" s="10">
+        <v>8.8</v>
+      </c>
+      <c r="Q220" s="11">
+        <v>0.376</v>
+      </c>
+      <c r="R220" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E221" s="3">
+        <v>1914</v>
+      </c>
+      <c r="F221" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="G221" s="3">
+        <v>1898</v>
+      </c>
+      <c r="H221" s="3">
+        <v>1898</v>
+      </c>
+      <c r="I221" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="J221" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N221" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="O221" s="2">
+        <v>1</v>
+      </c>
+      <c r="P221" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="Q221" s="11">
+        <v>0.179</v>
+      </c>
+      <c r="R221" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A222" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E222" s="7">
+        <v>3904</v>
+      </c>
+      <c r="F222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="G222" s="7">
+        <v>3848.6</v>
+      </c>
+      <c r="H222" s="7">
+        <v>3852</v>
+      </c>
+      <c r="I222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="J222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="K222" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M222" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="O222" s="6">
+        <v>1</v>
+      </c>
+      <c r="P222" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q222" s="9">
+        <v>0.286</v>
+      </c>
+      <c r="R222" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A223" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E223" s="7">
+        <v>418.75</v>
+      </c>
+      <c r="F223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="G223" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="H223" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="I223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="J223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="K223" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M223" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="O223" s="6">
+        <v>1</v>
+      </c>
+      <c r="P223" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="Q223" s="9">
+        <v>0.181</v>
+      </c>
+      <c r="R223" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A224" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E224" s="7">
+        <v>130.45</v>
+      </c>
+      <c r="F224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="G224" s="7">
+        <v>129.4</v>
+      </c>
+      <c r="H224" s="7">
+        <v>129.39</v>
+      </c>
+      <c r="I224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="J224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="K224" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M224" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="O224" s="6">
+        <v>1</v>
+      </c>
+      <c r="P224" s="8">
+        <v>0.14</v>
+      </c>
+      <c r="Q224" s="9">
+        <v>0.108</v>
+      </c>
+      <c r="R224" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E225" s="3">
+        <v>2050.3</v>
+      </c>
+      <c r="F225" s="3">
+        <v>2030.9</v>
+      </c>
+      <c r="G225" s="3">
+        <v>2038</v>
+      </c>
+      <c r="H225" s="3">
+        <v>2037.7</v>
+      </c>
+      <c r="I225" s="3">
+        <v>2030.9</v>
+      </c>
+      <c r="J225" s="3">
+        <v>2030.9</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N225" s="3">
+        <v>2030.9</v>
+      </c>
+      <c r="O225" s="2">
+        <v>1</v>
+      </c>
+      <c r="P225" s="10">
+        <v>6.8</v>
+      </c>
+      <c r="Q225" s="11">
+        <v>0.334</v>
+      </c>
+      <c r="R225" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A226" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E226" s="7">
+        <v>26285</v>
+      </c>
+      <c r="F226" s="7">
+        <v>25990</v>
+      </c>
+      <c r="G226" s="7">
+        <v>26085</v>
+      </c>
+      <c r="H226" s="7">
+        <v>26090</v>
+      </c>
+      <c r="I226" s="7">
+        <v>25990</v>
+      </c>
+      <c r="J226" s="7">
+        <v>25990</v>
+      </c>
+      <c r="K226" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L226" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M226" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N226" s="7">
+        <v>25990</v>
+      </c>
+      <c r="O226" s="6">
+        <v>1</v>
+      </c>
+      <c r="P226" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q226" s="9">
+        <v>0.383</v>
+      </c>
+      <c r="R226" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A227" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E227" s="7">
+        <v>455.55</v>
+      </c>
+      <c r="F227" s="7">
+        <v>450</v>
+      </c>
+      <c r="G227" s="7">
+        <v>451</v>
+      </c>
+      <c r="H227" s="7">
+        <v>451</v>
+      </c>
+      <c r="I227" s="7">
+        <v>450</v>
+      </c>
+      <c r="J227" s="7">
+        <v>450</v>
+      </c>
+      <c r="K227" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L227" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M227" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N227" s="7">
+        <v>450</v>
+      </c>
+      <c r="O227" s="6">
+        <v>1</v>
+      </c>
+      <c r="P227" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q227" s="9">
+        <v>0.222</v>
+      </c>
+      <c r="R227" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A228" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E228" s="7">
+        <v>125.75</v>
+      </c>
+      <c r="F228" s="7">
+        <v>125.07</v>
+      </c>
+      <c r="G228" s="7">
+        <v>125.16</v>
+      </c>
+      <c r="H228" s="7">
+        <v>122.14</v>
+      </c>
+      <c r="I228" s="7">
+        <v>125.07</v>
+      </c>
+      <c r="J228" s="7">
+        <v>119.21</v>
+      </c>
+      <c r="K228" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L228" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M228" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="N228" s="7">
+        <v>119.21</v>
+      </c>
+      <c r="O228" s="6">
+        <v>25</v>
+      </c>
+      <c r="P228" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="Q228" s="9">
+        <v>2.399</v>
+      </c>
+      <c r="R228" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E229" s="3">
+        <v>488.55</v>
+      </c>
+      <c r="F229" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="G229" s="3">
+        <v>485.55</v>
+      </c>
+      <c r="H229" s="3">
+        <v>468</v>
+      </c>
+      <c r="I229" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="J229" s="3">
+        <v>451.65</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="N229" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="O229" s="2">
+        <v>1</v>
+      </c>
+      <c r="P229" s="4">
+        <v>-16.35</v>
+      </c>
+      <c r="Q229" s="5">
+        <v>-3.494</v>
+      </c>
+      <c r="R229" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A230" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="E230" s="13">
+        <v>536.2</v>
+      </c>
+      <c r="F230" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="G230" s="13">
+        <v>533.25</v>
+      </c>
+      <c r="H230" s="13">
+        <v>502</v>
+      </c>
+      <c r="I230" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="J230" s="13">
+        <v>471.95</v>
+      </c>
+      <c r="K230" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L230" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M230" s="12"/>
+      <c r="N230" s="12"/>
+      <c r="O230" s="12"/>
+      <c r="P230" s="12"/>
+      <c r="Q230" s="12"/>
+      <c r="R230" s="12" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E231" s="3">
+        <v>654</v>
+      </c>
+      <c r="F231" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="G231" s="3">
+        <v>647.35</v>
+      </c>
+      <c r="H231" s="3">
+        <v>646.9</v>
+      </c>
+      <c r="I231" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="J231" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="N231" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="O231" s="2">
+        <v>1</v>
+      </c>
+      <c r="P231" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q231" s="11">
+        <v>0.085</v>
+      </c>
+      <c r="R231" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E232" s="3">
+        <v>1373.1</v>
+      </c>
+      <c r="F232" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="G232" s="3">
+        <v>1366.2</v>
+      </c>
+      <c r="H232" s="3">
+        <v>1366.1</v>
+      </c>
+      <c r="I232" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="J232" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="N232" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="O232" s="2">
+        <v>1</v>
+      </c>
+      <c r="P232" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="Q232" s="11">
+        <v>0.044</v>
+      </c>
+      <c r="R232" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E233" s="3">
+        <v>1278.8</v>
+      </c>
+      <c r="F233" s="3">
+        <v>1274</v>
+      </c>
+      <c r="G233" s="3">
+        <v>1276.6</v>
+      </c>
+      <c r="H233" s="3">
+        <v>1277.3</v>
+      </c>
+      <c r="I233" s="3">
+        <v>1274</v>
+      </c>
+      <c r="J233" s="3">
+        <v>1274</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L233" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M233" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="N233" s="3">
+        <v>1274</v>
+      </c>
+      <c r="O233" s="2">
+        <v>1</v>
+      </c>
+      <c r="P233" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q233" s="11">
+        <v>0.258</v>
+      </c>
+      <c r="R233" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E234" s="3">
+        <v>1280</v>
+      </c>
+      <c r="F234" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="G234" s="3">
+        <v>1276</v>
+      </c>
+      <c r="H234" s="3">
+        <v>1276.2</v>
+      </c>
+      <c r="I234" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="J234" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="N234" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="O234" s="2">
+        <v>1</v>
+      </c>
+      <c r="P234" s="10">
+        <v>1.1</v>
+      </c>
+      <c r="Q234" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R234" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E235" s="3">
+        <v>122.43</v>
+      </c>
+      <c r="F235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="G235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="H235" s="3">
+        <v>121.56</v>
+      </c>
+      <c r="I235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="J235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="K235" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L235" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M235" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="O235" s="2">
+        <v>1</v>
+      </c>
+      <c r="P235" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q235" s="11">
+        <v>0.041</v>
+      </c>
+      <c r="R235" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E236" s="3">
+        <v>3306.1</v>
+      </c>
+      <c r="F236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="G236" s="3">
+        <v>3285.9</v>
+      </c>
+      <c r="H236" s="3">
+        <v>3285.2</v>
+      </c>
+      <c r="I236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="J236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M236" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="O236" s="2">
+        <v>1</v>
+      </c>
+      <c r="P236" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="Q236" s="11">
+        <v>0.055</v>
+      </c>
+      <c r="R236" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A237" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E237" s="7">
+        <v>507.65</v>
+      </c>
+      <c r="F237" s="7">
+        <v>506.3</v>
+      </c>
+      <c r="G237" s="7">
+        <v>506.85</v>
+      </c>
+      <c r="H237" s="7">
+        <v>506.15</v>
+      </c>
+      <c r="I237" s="7">
+        <v>506.3</v>
+      </c>
+      <c r="J237" s="7">
+        <v>506</v>
+      </c>
+      <c r="K237" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L237" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M237" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="N237" s="7">
+        <v>506</v>
+      </c>
+      <c r="O237" s="6">
+        <v>1</v>
+      </c>
+      <c r="P237" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="Q237" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R237" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E238" s="3">
+        <v>7808</v>
+      </c>
+      <c r="F238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="G238" s="3">
+        <v>7780</v>
+      </c>
+      <c r="H238" s="3">
+        <v>7778.5</v>
+      </c>
+      <c r="I238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="J238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M238" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="N238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="O238" s="2">
+        <v>1</v>
+      </c>
+      <c r="P238" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q238" s="11">
+        <v>0.077</v>
+      </c>
+      <c r="R238" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A239" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="E239" s="7">
+        <v>1457.4</v>
+      </c>
+      <c r="F239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="G239" s="7">
+        <v>1450.7</v>
+      </c>
+      <c r="H239" s="7">
+        <v>1450.2</v>
+      </c>
+      <c r="I239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="J239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="K239" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L239" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M239" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="N239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="O239" s="6">
+        <v>1</v>
+      </c>
+      <c r="P239" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="Q239" s="9">
+        <v>0.014</v>
+      </c>
+      <c r="R239" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E240" s="3">
+        <v>96.29</v>
+      </c>
+      <c r="F240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="G240" s="3">
+        <v>95.77</v>
+      </c>
+      <c r="H240" s="3">
+        <v>95.77</v>
+      </c>
+      <c r="I240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="J240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M240" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="N240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="O240" s="2">
+        <v>1</v>
+      </c>
+      <c r="P240" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="Q240" s="11">
+        <v>0.125</v>
+      </c>
+      <c r="R240" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E241" s="3">
+        <v>963.5</v>
+      </c>
+      <c r="F241" s="3">
+        <v>957</v>
+      </c>
+      <c r="G241" s="3">
+        <v>957.4</v>
+      </c>
+      <c r="H241" s="3">
+        <v>957.4</v>
+      </c>
+      <c r="I241" s="3">
+        <v>957</v>
+      </c>
+      <c r="J241" s="3">
+        <v>957</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L241" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M241" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N241" s="3">
+        <v>957</v>
+      </c>
+      <c r="O241" s="2">
+        <v>1</v>
+      </c>
+      <c r="P241" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="Q241" s="11">
+        <v>0.042</v>
+      </c>
+      <c r="R241" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E242" s="3">
+        <v>2091.2</v>
+      </c>
+      <c r="F242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="G242" s="3">
+        <v>2078.4</v>
+      </c>
+      <c r="H242" s="3">
+        <v>2077.5</v>
+      </c>
+      <c r="I242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="J242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="K242" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M242" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="O242" s="2">
+        <v>1</v>
+      </c>
+      <c r="P242" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="Q242" s="11">
+        <v>0.111</v>
+      </c>
+      <c r="R242" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E243" s="3">
+        <v>9730</v>
+      </c>
+      <c r="F243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="G243" s="3">
+        <v>9668</v>
+      </c>
+      <c r="H243" s="3">
+        <v>9668</v>
+      </c>
+      <c r="I243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="J243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M243" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="O243" s="2">
+        <v>1</v>
+      </c>
+      <c r="P243" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q243" s="11">
+        <v>0.052</v>
+      </c>
+      <c r="R243" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E244" s="3">
+        <v>373.95</v>
+      </c>
+      <c r="F244" s="3">
+        <v>372</v>
+      </c>
+      <c r="G244" s="3">
+        <v>372.2</v>
+      </c>
+      <c r="H244" s="3">
+        <v>372.25</v>
+      </c>
+      <c r="I244" s="3">
+        <v>372</v>
+      </c>
+      <c r="J244" s="3">
+        <v>372</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L244" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M244" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="N244" s="3">
+        <v>372</v>
+      </c>
+      <c r="O244" s="2">
+        <v>1</v>
+      </c>
+      <c r="P244" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="Q244" s="11">
+        <v>0.067</v>
+      </c>
+      <c r="R244" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E245" s="3">
+        <v>526.05</v>
+      </c>
+      <c r="F245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="G245" s="3">
+        <v>523.9</v>
+      </c>
+      <c r="H245" s="3">
+        <v>523.9</v>
+      </c>
+      <c r="I245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="J245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="K245" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L245" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M245" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="N245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="O245" s="2">
+        <v>1</v>
+      </c>
+      <c r="P245" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q245" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="R245" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E246" s="3">
+        <v>609.05</v>
+      </c>
+      <c r="F246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="G246" s="3">
+        <v>606.8</v>
+      </c>
+      <c r="H246" s="3">
+        <v>606.8</v>
+      </c>
+      <c r="I246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="J246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="K246" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L246" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M246" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="N246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="O246" s="2">
+        <v>1</v>
+      </c>
+      <c r="P246" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q246" s="11">
+        <v>0.008</v>
+      </c>
+      <c r="R246" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E247" s="3">
+        <v>401.2</v>
+      </c>
+      <c r="F247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="G247" s="3">
+        <v>399.2</v>
+      </c>
+      <c r="H247" s="3">
+        <v>399.25</v>
+      </c>
+      <c r="I247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="J247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="K247" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L247" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M247" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="N247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="O247" s="2">
+        <v>1</v>
+      </c>
+      <c r="P247" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q247" s="11">
+        <v>0.138</v>
+      </c>
+      <c r="R247" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E248" s="3">
+        <v>1242.6</v>
+      </c>
+      <c r="F248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="G248" s="3">
+        <v>1235.6</v>
+      </c>
+      <c r="H248" s="3">
+        <v>1236.3</v>
+      </c>
+      <c r="I248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="J248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M248" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="N248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="O248" s="2">
+        <v>1</v>
+      </c>
+      <c r="P248" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="Q248" s="11">
+        <v>0.105</v>
+      </c>
+      <c r="R248" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E249" s="3">
+        <v>1202.9</v>
+      </c>
+      <c r="F249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="G249" s="3">
+        <v>1188.3</v>
+      </c>
+      <c r="H249" s="3">
+        <v>1188.4</v>
+      </c>
+      <c r="I249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="J249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="K249" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M249" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="O249" s="2">
+        <v>1</v>
+      </c>
+      <c r="P249" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q249" s="11">
+        <v>0.421</v>
+      </c>
+      <c r="R249" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E250" s="3">
+        <v>1870</v>
+      </c>
+      <c r="F250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="G250" s="3">
+        <v>1841.4</v>
+      </c>
+      <c r="H250" s="3">
+        <v>1840.4</v>
+      </c>
+      <c r="I250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="J250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="K250" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L250" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M250" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="O250" s="2">
+        <v>1</v>
+      </c>
+      <c r="P250" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="Q250" s="11">
+        <v>0.402</v>
+      </c>
+      <c r="R250" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E251" s="3">
+        <v>2203.6</v>
+      </c>
+      <c r="F251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="G251" s="3">
+        <v>2192.8</v>
+      </c>
+      <c r="H251" s="3">
+        <v>2192.6</v>
+      </c>
+      <c r="I251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="J251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="K251" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M251" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="O251" s="2">
+        <v>1</v>
+      </c>
+      <c r="P251" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="Q251" s="11">
+        <v>0.328</v>
+      </c>
+      <c r="R251" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E252" s="3">
+        <v>4728.8</v>
+      </c>
+      <c r="F252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="G252" s="3">
+        <v>4710.4</v>
+      </c>
+      <c r="H252" s="3">
+        <v>4703.3</v>
+      </c>
+      <c r="I252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="J252" s="3">
+        <v>4701.7</v>
+      </c>
+      <c r="K252" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M252" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="N252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="O252" s="2">
+        <v>1</v>
+      </c>
+      <c r="P252" s="4">
+        <v>-1.6</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>-0.034</v>
+      </c>
+      <c r="R252" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E253" s="3">
+        <v>70.31</v>
+      </c>
+      <c r="F253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="G253" s="3">
+        <v>70.1</v>
+      </c>
+      <c r="H253" s="3">
+        <v>70.08</v>
+      </c>
+      <c r="I253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="J253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="K253" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M253" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="N253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="O253" s="2">
+        <v>1</v>
+      </c>
+      <c r="P253" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="Q253" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R253" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="E254" s="7">
+        <v>961.35</v>
+      </c>
+      <c r="F254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="G254" s="7">
+        <v>949.25</v>
+      </c>
+      <c r="H254" s="7">
+        <v>949.05</v>
+      </c>
+      <c r="I254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="J254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="K254" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M254" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="N254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="O254" s="6">
+        <v>1</v>
+      </c>
+      <c r="P254" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="Q254" s="9">
+        <v>0.205</v>
+      </c>
+      <c r="R254" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E255" s="3">
+        <v>165.26</v>
+      </c>
+      <c r="F255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="G255" s="3">
+        <v>162.38</v>
+      </c>
+      <c r="H255" s="3">
+        <v>162.4</v>
+      </c>
+      <c r="I255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="J255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="K255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M255" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="O255" s="2">
+        <v>1</v>
+      </c>
+      <c r="P255" s="10">
+        <v>0.37</v>
+      </c>
+      <c r="Q255" s="11">
+        <v>0.228</v>
+      </c>
+      <c r="R255" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E256" s="3">
+        <v>1253.9</v>
+      </c>
+      <c r="F256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="G256" s="3">
+        <v>1217</v>
+      </c>
+      <c r="H256" s="3">
+        <v>1218</v>
+      </c>
+      <c r="I256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="J256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="K256" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M256" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="O256" s="2">
+        <v>1</v>
+      </c>
+      <c r="P256" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="Q256" s="11">
+        <v>0.222</v>
+      </c>
+      <c r="R256" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E257" s="3">
+        <v>396.3</v>
+      </c>
+      <c r="F257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="G257" s="3">
+        <v>392.55</v>
+      </c>
+      <c r="H257" s="3">
+        <v>392.45</v>
+      </c>
+      <c r="I257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="J257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="K257" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L257" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M257" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="O257" s="2">
+        <v>1</v>
+      </c>
+      <c r="P257" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="Q257" s="11">
+        <v>0.612</v>
+      </c>
+      <c r="R257" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E258" s="3">
+        <v>1649.4</v>
+      </c>
+      <c r="F258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="G258" s="3">
+        <v>1627.1</v>
+      </c>
+      <c r="H258" s="3">
+        <v>1628</v>
+      </c>
+      <c r="I258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="J258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M258" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="O258" s="2">
+        <v>1</v>
+      </c>
+      <c r="P258" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="Q258" s="11">
+        <v>0.227</v>
+      </c>
+      <c r="R258" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E259" s="3">
+        <v>258.95</v>
+      </c>
+      <c r="F259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="G259" s="3">
+        <v>253.5</v>
+      </c>
+      <c r="H259" s="3">
+        <v>253.45</v>
+      </c>
+      <c r="I259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="J259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="K259" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M259" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="O259" s="2">
+        <v>1</v>
+      </c>
+      <c r="P259" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="Q259" s="11">
+        <v>0.375</v>
+      </c>
+      <c r="R259" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E260" s="3">
+        <v>1340.9</v>
+      </c>
+      <c r="F260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="G260" s="3">
+        <v>1329</v>
+      </c>
+      <c r="H260" s="3">
+        <v>1328.9</v>
+      </c>
+      <c r="I260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="J260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L260" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M260" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="N260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="O260" s="2">
+        <v>1</v>
+      </c>
+      <c r="P260" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="Q260" s="11">
+        <v>0.008</v>
+      </c>
+      <c r="R260" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E261" s="3">
+        <v>980.15</v>
+      </c>
+      <c r="F261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="G261" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="H261" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="I261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="J261" s="3">
+        <v>990.1</v>
+      </c>
+      <c r="K261" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L261" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M261" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="N261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="O261" s="2">
+        <v>22</v>
+      </c>
+      <c r="P261" s="4">
+        <v>-12.2</v>
+      </c>
+      <c r="Q261" s="5">
+        <v>-1.248</v>
+      </c>
+      <c r="R261" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E262" s="3">
+        <v>1235</v>
+      </c>
+      <c r="F262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="G262" s="3">
+        <v>1233.1</v>
+      </c>
+      <c r="H262" s="3">
+        <v>1233</v>
+      </c>
+      <c r="I262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="J262" s="3">
+        <v>1245.7</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L262" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M262" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="N262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="O262" s="2">
+        <v>1</v>
+      </c>
+      <c r="P262" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="Q262" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="R262" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A263" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E263" s="7">
+        <v>1327.9</v>
+      </c>
+      <c r="F263" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="G263" s="7">
+        <v>1324.6</v>
+      </c>
+      <c r="H263" s="7">
+        <v>1323.7</v>
+      </c>
+      <c r="I263" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="J263" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="K263" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L263" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M263" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="N263" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="O263" s="6">
+        <v>2</v>
+      </c>
+      <c r="P263" s="8">
+        <v>47.6</v>
+      </c>
+      <c r="Q263" s="9">
+        <v>3.596</v>
+      </c>
+      <c r="R263" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A264" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D264" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E264" s="13">
+        <v>469.7</v>
+      </c>
+      <c r="F264" s="13">
+        <v>460.35</v>
+      </c>
+      <c r="G264" s="13">
+        <v>468.65</v>
+      </c>
+      <c r="H264" s="13">
+        <v>468.6</v>
+      </c>
+      <c r="I264" s="13">
+        <v>460.35</v>
+      </c>
+      <c r="J264" s="13">
+        <v>476.85</v>
+      </c>
+      <c r="K264" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L264" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M264" s="12"/>
+      <c r="N264" s="12"/>
+      <c r="O264" s="12"/>
+      <c r="P264" s="12"/>
+      <c r="Q264" s="12"/>
+      <c r="R264" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A265" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="B265" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="C155" s="12" t="s">
+      <c r="C265" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D155" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E155" s="13">
-        <v>2088.9</v>
-      </c>
-      <c r="F155" s="13">
-        <v>2079.2</v>
-      </c>
-      <c r="G155" s="13">
-        <v>2086.7</v>
-      </c>
-      <c r="H155" s="13">
-        <v>2086.7</v>
-      </c>
-      <c r="I155" s="13">
-        <v>2079.2</v>
-      </c>
-      <c r="J155" s="13">
-        <v>2094.2</v>
-      </c>
-      <c r="K155" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L155" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M155" s="12"/>
-      <c r="N155" s="12"/>
-      <c r="O155" s="12"/>
-      <c r="P155" s="12"/>
-      <c r="Q155" s="12"/>
-      <c r="R155" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A156" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C156" s="12" t="s">
+      <c r="D265" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E265" s="13">
+        <v>2135.5</v>
+      </c>
+      <c r="F265" s="13">
+        <v>2094.4</v>
+      </c>
+      <c r="G265" s="13">
+        <v>2131.5</v>
+      </c>
+      <c r="H265" s="13">
+        <v>2131</v>
+      </c>
+      <c r="I265" s="13">
+        <v>2094.4</v>
+      </c>
+      <c r="J265" s="13">
+        <v>2167.6</v>
+      </c>
+      <c r="K265" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L265" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M265" s="12"/>
+      <c r="N265" s="12"/>
+      <c r="O265" s="12"/>
+      <c r="P265" s="12"/>
+      <c r="Q265" s="12"/>
+      <c r="R265" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A266" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C266" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D156" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E156" s="13">
-        <v>510.4</v>
-      </c>
-      <c r="F156" s="13">
-        <v>506.3</v>
-      </c>
-      <c r="G156" s="13">
-        <v>509.4</v>
-      </c>
-      <c r="H156" s="13">
-        <v>509.4</v>
-      </c>
-      <c r="I156" s="13">
-        <v>506.3</v>
-      </c>
-      <c r="J156" s="13">
-        <v>512.5</v>
-      </c>
-      <c r="K156" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L156" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M156" s="12"/>
-      <c r="N156" s="12"/>
-      <c r="O156" s="12"/>
-      <c r="P156" s="12"/>
-      <c r="Q156" s="12"/>
-      <c r="R156" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A157" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C157" s="12" t="s">
+      <c r="D266" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E266" s="7">
+        <v>2476</v>
+      </c>
+      <c r="F266" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="G266" s="7">
+        <v>2457.7</v>
+      </c>
+      <c r="H266" s="7">
+        <v>2457.9</v>
+      </c>
+      <c r="I266" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="J266" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="K266" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L266" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M266" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="N266" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="O266" s="6">
+        <v>1</v>
+      </c>
+      <c r="P266" s="8">
+        <v>87.8</v>
+      </c>
+      <c r="Q266" s="9">
+        <v>3.572</v>
+      </c>
+      <c r="R266" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A267" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C267" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D157" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E157" s="13">
-        <v>624.1</v>
-      </c>
-      <c r="F157" s="13">
-        <v>618.45</v>
-      </c>
-      <c r="G157" s="13">
+      <c r="D267" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E267" s="13">
+        <v>8628</v>
+      </c>
+      <c r="F267" s="13">
+        <v>8480</v>
+      </c>
+      <c r="G267" s="13">
+        <v>8621</v>
+      </c>
+      <c r="H267" s="13">
+        <v>8621</v>
+      </c>
+      <c r="I267" s="13">
+        <v>8480</v>
+      </c>
+      <c r="J267" s="13">
+        <v>8762</v>
+      </c>
+      <c r="K267" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L267" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M267" s="12"/>
+      <c r="N267" s="12"/>
+      <c r="O267" s="12"/>
+      <c r="P267" s="12"/>
+      <c r="Q267" s="12"/>
+      <c r="R267" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A268" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D268" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E268" s="13">
+        <v>1415.7</v>
+      </c>
+      <c r="F268" s="13">
+        <v>1390.3</v>
+      </c>
+      <c r="G268" s="13">
+        <v>1414.6</v>
+      </c>
+      <c r="H268" s="13">
+        <v>1414.7</v>
+      </c>
+      <c r="I268" s="13">
+        <v>1390.3</v>
+      </c>
+      <c r="J268" s="13">
+        <v>1439.1</v>
+      </c>
+      <c r="K268" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L268" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M268" s="12"/>
+      <c r="N268" s="12"/>
+      <c r="O268" s="12"/>
+      <c r="P268" s="12"/>
+      <c r="Q268" s="12"/>
+      <c r="R268" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A269" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D269" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E269" s="13">
+        <v>382.25</v>
+      </c>
+      <c r="F269" s="13">
+        <v>373.1</v>
+      </c>
+      <c r="G269" s="13">
+        <v>382.1</v>
+      </c>
+      <c r="H269" s="13">
+        <v>382.25</v>
+      </c>
+      <c r="I269" s="13">
+        <v>373.1</v>
+      </c>
+      <c r="J269" s="13">
+        <v>391.4</v>
+      </c>
+      <c r="K269" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L269" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M269" s="12"/>
+      <c r="N269" s="12"/>
+      <c r="O269" s="12"/>
+      <c r="P269" s="12"/>
+      <c r="Q269" s="12"/>
+      <c r="R269" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A270" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E270" s="7">
+        <v>4344.9</v>
+      </c>
+      <c r="F270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="G270" s="7">
+        <v>4339.9</v>
+      </c>
+      <c r="H270" s="7">
+        <v>4339.9</v>
+      </c>
+      <c r="I270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="J270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="K270" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L270" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M270" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="N270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="O270" s="6">
+        <v>1</v>
+      </c>
+      <c r="P270" s="8">
+        <v>4.9</v>
+      </c>
+      <c r="Q270" s="9">
+        <v>0.113</v>
+      </c>
+      <c r="R270" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A271" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D271" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="E271" s="13">
+        <v>3903.9</v>
+      </c>
+      <c r="F271" s="13">
+        <v>3861.2</v>
+      </c>
+      <c r="G271" s="13">
+        <v>3890</v>
+      </c>
+      <c r="H271" s="13">
+        <v>3890.8</v>
+      </c>
+      <c r="I271" s="13">
+        <v>3861.2</v>
+      </c>
+      <c r="J271" s="13">
+        <v>3920.4</v>
+      </c>
+      <c r="K271" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L271" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M271" s="12"/>
+      <c r="N271" s="12"/>
+      <c r="O271" s="12"/>
+      <c r="P271" s="12"/>
+      <c r="Q271" s="12"/>
+      <c r="R271" s="12" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A272" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="E272" s="7">
+        <v>1885.1</v>
+      </c>
+      <c r="F272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="G272" s="7">
+        <v>1879.1</v>
+      </c>
+      <c r="H272" s="7">
+        <v>1879.1</v>
+      </c>
+      <c r="I272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="J272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="K272" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L272" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M272" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="N272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="O272" s="6">
+        <v>1</v>
+      </c>
+      <c r="P272" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="Q272" s="9">
+        <v>0.005</v>
+      </c>
+      <c r="R272" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E273" s="3">
+        <v>6013</v>
+      </c>
+      <c r="F273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="G273" s="3">
+        <v>6002.5</v>
+      </c>
+      <c r="H273" s="3">
+        <v>6005.5</v>
+      </c>
+      <c r="I273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="J273" s="3">
+        <v>6020.5</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L273" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M273" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="N273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="O273" s="2">
+        <v>1</v>
+      </c>
+      <c r="P273" s="4">
+        <v>-15</v>
+      </c>
+      <c r="Q273" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="R273" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A274" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="C274" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D274" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="E274" s="13">
+        <v>2126.1</v>
+      </c>
+      <c r="F274" s="13">
+        <v>2118.3</v>
+      </c>
+      <c r="G274" s="13">
+        <v>2126.1</v>
+      </c>
+      <c r="H274" s="13">
+        <v>2125.6</v>
+      </c>
+      <c r="I274" s="13">
+        <v>2118.3</v>
+      </c>
+      <c r="J274" s="13">
+        <v>2132.9</v>
+      </c>
+      <c r="K274" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L274" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M274" s="12"/>
+      <c r="N274" s="12"/>
+      <c r="O274" s="12"/>
+      <c r="P274" s="12"/>
+      <c r="Q274" s="12"/>
+      <c r="R274" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A275" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="H157" s="13">
-        <v>624.1</v>
-      </c>
-      <c r="I157" s="13">
-        <v>618.45</v>
-      </c>
-      <c r="J157" s="13">
-        <v>629.75</v>
-      </c>
-      <c r="K157" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L157" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M157" s="12"/>
-      <c r="N157" s="12"/>
-      <c r="O157" s="12"/>
-      <c r="P157" s="12"/>
-      <c r="Q157" s="12"/>
-      <c r="R157" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A158" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C158" s="12" t="s">
+      <c r="B275" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C275" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D158" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E158" s="13">
-        <v>542.7</v>
-      </c>
-      <c r="F158" s="13">
-        <v>540.05</v>
-      </c>
-      <c r="G158" s="13">
-        <v>541.25</v>
-      </c>
-      <c r="H158" s="13">
-        <v>541.55</v>
-      </c>
-      <c r="I158" s="13">
-        <v>540.05</v>
-      </c>
-      <c r="J158" s="13">
-        <v>543.05</v>
-      </c>
-      <c r="K158" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L158" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M158" s="12"/>
-      <c r="N158" s="12"/>
-      <c r="O158" s="12"/>
-      <c r="P158" s="12"/>
-      <c r="Q158" s="12"/>
-      <c r="R158" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A160" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="P160" s="15">
-        <v>530.67</v>
-      </c>
-      <c r="R160" s="14" t="s">
-        <v>406</v>
+      <c r="D275" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="E275" s="13">
+        <v>117.6</v>
+      </c>
+      <c r="F275" s="13">
+        <v>116.64</v>
+      </c>
+      <c r="G275" s="13">
+        <v>117.54</v>
+      </c>
+      <c r="H275" s="13">
+        <v>117.54</v>
+      </c>
+      <c r="I275" s="13">
+        <v>116.64</v>
+      </c>
+      <c r="J275" s="13">
+        <v>118.44</v>
+      </c>
+      <c r="K275" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L275" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M275" s="12"/>
+      <c r="N275" s="12"/>
+      <c r="O275" s="12"/>
+      <c r="P275" s="12"/>
+      <c r="Q275" s="12"/>
+      <c r="R275" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A276" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D276" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="E276" s="13">
+        <v>2190.3</v>
+      </c>
+      <c r="F276" s="13">
+        <v>2180.9</v>
+      </c>
+      <c r="G276" s="13">
+        <v>2182</v>
+      </c>
+      <c r="H276" s="12"/>
+      <c r="I276" s="13">
+        <v>2180.9</v>
+      </c>
+      <c r="J276" s="12"/>
+      <c r="K276" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L276" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M276" s="12"/>
+      <c r="N276" s="12"/>
+      <c r="O276" s="12"/>
+      <c r="P276" s="12"/>
+      <c r="Q276" s="12"/>
+      <c r="R276" s="12" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A277" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C277" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D277" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="E277" s="13">
+        <v>790.15</v>
+      </c>
+      <c r="F277" s="13">
+        <v>784.05</v>
+      </c>
+      <c r="G277" s="13">
+        <v>789.95</v>
+      </c>
+      <c r="H277" s="12"/>
+      <c r="I277" s="13">
+        <v>784.05</v>
+      </c>
+      <c r="J277" s="12"/>
+      <c r="K277" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L277" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M277" s="12"/>
+      <c r="N277" s="12"/>
+      <c r="O277" s="12"/>
+      <c r="P277" s="12"/>
+      <c r="Q277" s="12"/>
+      <c r="R277" s="12" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E278" s="3">
+        <v>422.45</v>
+      </c>
+      <c r="F278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="G278" s="3">
+        <v>421.75</v>
+      </c>
+      <c r="H278" s="3">
+        <v>422</v>
+      </c>
+      <c r="I278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="J278" s="3">
+        <v>431.8</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L278" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M278" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="N278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="O278" s="2">
+        <v>16</v>
+      </c>
+      <c r="P278" s="4">
+        <v>-9.8</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>-2.322</v>
+      </c>
+      <c r="R278" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A280" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="P280" s="15">
+        <v>529.16</v>
+      </c>
+      <c r="R280" s="14" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>
